--- a/Assets/StreamingAssets/Excel/InGameEventConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/InGameEventConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\Unity\Projects\WindowsSurvival\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37BE4E7-85DB-40E4-A0D2-6C5F5CDAC38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7274F63-30C3-4346-AFAE-3A67F4824F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>事件名</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>恒星食</t>
-  </si>
-  <si>
-    <t>健忘症</t>
   </si>
   <si>
     <t>一氧化碳爆炸</t>
@@ -428,14 +425,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E198"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="13.69921875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.7109375" style="1"/>
+    <col min="1" max="3" width="13.69921875" style="1"/>
     <col min="4" max="4" width="27" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="13.7109375" style="1"/>
+    <col min="5" max="16384" width="13.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,7 +449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -469,7 +466,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -483,7 +480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -500,7 +497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -517,7 +514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -534,7 +531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -551,7 +548,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -565,7 +562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -582,7 +579,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -596,7 +593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -604,619 +601,605 @@
         <v>4</v>
       </c>
       <c r="C11" s="1">
-        <v>0.2</v>
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="E11" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2">
         <v>-4</v>
       </c>
       <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>1.5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2">
-        <v>-4</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B30" s="2"/>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B31" s="2"/>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B33" s="2"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B46" s="2"/>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B47" s="2"/>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B48" s="2"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B54" s="2"/>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B58" s="2"/>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B59" s="2"/>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B64" s="2"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B65" s="2"/>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B67" s="2"/>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B68" s="2"/>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B69" s="2"/>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B70" s="2"/>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B71" s="2"/>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B72" s="2"/>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B73" s="2"/>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B74" s="2"/>
     </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B75" s="2"/>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B77" s="2"/>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B79" s="2"/>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B81" s="2"/>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B83" s="2"/>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B84" s="2"/>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B85" s="2"/>
     </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B86" s="2"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B87" s="2"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B89" s="2"/>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
     </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B92" s="2"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
     </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B94" s="2"/>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B95" s="2"/>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B97" s="2"/>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B98" s="2"/>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B99" s="2"/>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B100" s="2"/>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B101" s="2"/>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B102" s="2"/>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B103" s="2"/>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B104" s="2"/>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B105" s="2"/>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B106" s="2"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B107" s="2"/>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B108" s="2"/>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B109" s="2"/>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B110" s="2"/>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B111" s="2"/>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B112" s="2"/>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="113" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B113" s="2"/>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="114" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B114" s="2"/>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="115" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B115" s="2"/>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="116" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B116" s="2"/>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="117" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B117" s="2"/>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B118" s="2"/>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B119" s="2"/>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B120" s="2"/>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B121" s="2"/>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="122" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B122" s="2"/>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="123" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B123" s="2"/>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="124" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B124" s="2"/>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="125" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B125" s="2"/>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="126" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B126" s="2"/>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B127" s="2"/>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="128" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B128" s="2"/>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="129" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B129" s="2"/>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="130" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B130" s="2"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="131" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B131" s="2"/>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="132" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B132" s="2"/>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="133" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B133" s="2"/>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="134" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B134" s="2"/>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="135" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B135" s="2"/>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="136" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B136" s="2"/>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="137" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B137" s="2"/>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="138" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B138" s="2"/>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="139" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B139" s="2"/>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="140" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B140" s="2"/>
     </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="141" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B141" s="2"/>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="142" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B142" s="2"/>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="143" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B143" s="2"/>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="144" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B144" s="2"/>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B145" s="2"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B146" s="2"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B147" s="2"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B148" s="2"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B149" s="2"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B150" s="2"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B151" s="2"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="152" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B152" s="2"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B153" s="2"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B154" s="2"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B155" s="2"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B156" s="2"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B157" s="2"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B158" s="2"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B159" s="2"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="160" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B160" s="2"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B161" s="2"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B162" s="2"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B163" s="2"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B164" s="2"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B165" s="2"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B166" s="2"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B167" s="2"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="168" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B168" s="2"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B169" s="2"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B170" s="2"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B171" s="2"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B172" s="2"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B173" s="2"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B174" s="2"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B175" s="2"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="176" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B176" s="2"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B177" s="2"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B178" s="2"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B179" s="2"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B180" s="2"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="181" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B181" s="2"/>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B182" s="2"/>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B183" s="2"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="184" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B184" s="2"/>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B185" s="2"/>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B186" s="2"/>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B187" s="2"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="188" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B188" s="2"/>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B189" s="2"/>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B190" s="2"/>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B192" s="2"/>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="193" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B193" s="2"/>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="194" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B194" s="2"/>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B195" s="2"/>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B196" s="2"/>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B197" s="2"/>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="198" spans="2:2" ht="13" x14ac:dyDescent="0.25">
       <c r="B198" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B1048576 B2:B13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"0,-3,-2,-1,1,2,3,4,-4,"</formula1>
     </dataValidation>
   </dataValidations>
